--- a/other/class_timetable/1.xlsx
+++ b/other/class_timetable/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\myProject\demo\other\class_timetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE57525-956E-4E8B-81CD-F67B85518F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBAD270-D05C-41D9-A3A1-59484B2FB7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="110">
   <si>
     <r>
       <rPr>
@@ -1630,7 +1630,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1645,11 +1645,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D04F"/>
       </patternFill>
     </fill>
     <fill>
@@ -1683,7 +1678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1732,9 +1727,6 @@
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1753,38 +1745,38 @@
     <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2151,127 +2143,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
     </row>
     <row r="2" spans="1:32" ht="12" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30" t="s">
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30" t="s">
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="31" t="s">
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
     </row>
     <row r="3" spans="1:32" ht="43.5" customHeight="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="33" t="s">
+      <c r="M3" s="23" t="s">
         <v>109</v>
       </c>
       <c r="N3" s="5" t="s">
@@ -2289,7 +2281,7 @@
       <c r="R3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="S3" s="20" t="s">
         <v>106</v>
       </c>
       <c r="T3" s="5" t="s">
@@ -2301,7 +2293,7 @@
       <c r="V3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="W3" s="22" t="s">
+      <c r="W3" s="21" t="s">
         <v>107</v>
       </c>
       <c r="X3" s="5" t="s">
@@ -2333,38 +2325,38 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="12" customHeight="1">
-      <c r="A4" s="26"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="27"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="31"/>
     </row>
     <row r="5" spans="1:32" ht="20" customHeight="1">
       <c r="A5" s="3"/>
@@ -2437,27 +2429,37 @@
       <c r="J6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="22" t="s">
         <v>108</v>
       </c>
       <c r="L6" s="15">
         <v>206</v>
       </c>
-      <c r="M6" s="16"/>
+      <c r="M6" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="N6" s="13" t="s">
         <v>47</v>
       </c>
       <c r="O6" s="14"/>
-      <c r="P6" s="16"/>
+      <c r="P6" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
-      <c r="S6" s="16"/>
+      <c r="S6" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="T6" s="14"/>
-      <c r="U6" s="16"/>
+      <c r="U6" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="V6" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="W6" s="16"/>
+      <c r="W6" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="X6" s="14"/>
       <c r="Y6" s="14"/>
       <c r="Z6" s="13" t="s">
@@ -2474,12 +2476,14 @@
       <c r="AE6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AF6" s="16"/>
+      <c r="AF6" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="7" spans="1:32" ht="12" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="9">
@@ -2495,7 +2499,7 @@
         <v>56</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="16" t="s">
         <v>57</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -2509,7 +2513,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
+      <c r="Q7" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
@@ -2534,13 +2540,13 @@
       <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <v>20104</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="18">
         <v>6</v>
       </c>
       <c r="E8" s="13" t="s">
@@ -2596,10 +2602,10 @@
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>20104</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="9">
@@ -2615,7 +2621,7 @@
         <v>75</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="16" t="s">
         <v>76</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -2632,14 +2638,18 @@
         <v>80</v>
       </c>
       <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+      <c r="P9" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="1" t="s">
         <v>81</v>
       </c>
       <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
+      <c r="U9" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="V9" s="1" t="s">
         <v>82</v>
       </c>
@@ -2651,23 +2661,29 @@
       <c r="Z9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AA9" s="3"/>
+      <c r="AA9" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
+      <c r="AD9" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="AE9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AF9" s="3"/>
+      <c r="AF9" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:32" ht="12" customHeight="1">
       <c r="A10" s="9">
         <v>2</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>10019</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>86</v>
       </c>
       <c r="D10" s="9">
@@ -2683,7 +2699,7 @@
         <v>89</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="16" t="s">
         <v>90</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -2722,10 +2738,10 @@
       <c r="A11" s="9">
         <v>3</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <v>10148</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>95</v>
       </c>
       <c r="D11" s="9">
@@ -2741,7 +2757,7 @@
         <v>98</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="16" t="s">
         <v>99</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -2782,10 +2798,10 @@
       <c r="A12" s="9">
         <v>5</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="19">
         <v>22162</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>105</v>
       </c>
       <c r="D12" s="9">
@@ -2821,151 +2837,143 @@
       <c r="AF12" s="3"/>
     </row>
     <row r="13" spans="1:32" ht="10.5" customHeight="1">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
     </row>
     <row r="14" spans="1:32" ht="21" customHeight="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
     </row>
     <row r="15" spans="1:32" ht="31.5" customHeight="1">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29"/>
     </row>
     <row r="16" spans="1:32" ht="10.45" customHeight="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="29"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="29"/>
+      <c r="AF16" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:V2"/>
-    <mergeCell ref="W2:AC2"/>
-    <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="A15:AF15"/>
     <mergeCell ref="A16:AF16"/>
     <mergeCell ref="K3:K4"/>
@@ -2982,6 +2990,14 @@
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="W2:AC2"/>
+    <mergeCell ref="AD2:AF2"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
